--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/15gps/back_15gps_summary.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/15gps/back_15gps_summary.xlsx
@@ -14,12 +14,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Velocity (m/s)</t>
   </si>
   <si>
     <t>Q_steady (W)</t>
+  </si>
+  <si>
+    <t>Q_uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -351,71 +354,95 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>217.3711893795659</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>217.5197871817224</v>
+      </c>
+      <c r="C2">
+        <v>24.09943133237424</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>389.1123109761087</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>389.17826830836</v>
+      </c>
+      <c r="C3">
+        <v>24.12852993862252</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>503.1047816204058</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>502.7327294678793</v>
+      </c>
+      <c r="C4">
+        <v>24.24868057004817</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>578.7331375234745</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>578.4433571466049</v>
+      </c>
+      <c r="C5">
+        <v>24.35054470079342</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>642.5360960986419</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>642.365926539937</v>
+      </c>
+      <c r="C6">
+        <v>24.47006440626338</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>679.0368946356135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>679.0002490210588</v>
+      </c>
+      <c r="C7">
+        <v>24.55416525093069</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>712.1263486527164</v>
+        <v>712.1522479382535</v>
+      </c>
+      <c r="C8">
+        <v>24.64700720281429</v>
       </c>
     </row>
   </sheetData>
